--- a/forms/trg/Formulir_TRG_dlp-rg.xlsx
+++ b/forms/trg/Formulir_TRG_dlp-rg.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B31)</f>
+        <f>COUNTA(Anggota!B5:B32)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F31)</f>
+        <f>COUNTA(Anggota!F5:F32)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,41 +925,37 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Kadarudin, S.H., M.H.</t>
+          <t>Prof. Dr. Iin Karita Sakharina, S.H., M.A.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>International Law, Human Rights Law, Refugee Law</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>International Law, Human Rights Law, Diplomatic Law</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>my-orcid?orcid=0000-0002-4919-6169</t>
-        </is>
-      </c>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>5996291</t>
+          <t>6041015</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57203506496</t>
+          <t>57216819104</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -974,17 +970,17 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Mutiah Wenda Juniar, S.H., LL.M.</t>
+          <t>Dr. Kadarudin, S.H., M.H.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>International Law, Disability Rights Law</t>
+          <t>International Law, Human Rights Law, Refugee Law</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -996,9 +992,21 @@
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="n"/>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>my-orcid?orcid=0000-0002-4919-6169</t>
+        </is>
+      </c>
+      <c r="K6" s="11" t="inlineStr">
+        <is>
+          <t>5996291</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>57203506496</t>
+        </is>
+      </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1011,17 +1019,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Rastiawaty, S.H., M.H.</t>
+          <t>Mutiah Wenda Juniar, S.H., LL.M.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Law and Society</t>
+          <t>International Law, Disability Rights Law</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -1048,22 +1056,22 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Stephen Rosenbaum</t>
+          <t>Rastiawaty, S.H., M.H.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Human Rights Law, Antidiscrimination Law, Disability Rights Law</t>
+          <t>Law and Society</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>University of California</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1085,22 +1093,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Honorio da Costa Fernandes Hornai</t>
+          <t>Stephen Rosenbaum</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>International Law</t>
+          <t>Human Rights Law, Antidiscrimination Law, Disability Rights Law</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>University of California</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1122,20 +1130,24 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Harry Arfhan</t>
+          <t>Honorio da Costa Fernandes Hornai</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
+          <t>International Law</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E10" s="11" t="n"/>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
@@ -1155,24 +1167,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Yuliani Azis</t>
+          <t>Harry Arfhan</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Medical Science</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
           <t>Hasanuddin University</t>
         </is>
       </c>
+      <c r="E11" s="11" t="n"/>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
@@ -1192,12 +1200,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Tasya Aisyah Pratiwi Maasba</t>
+          <t>Yuliani Azis</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1229,17 +1237,17 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Edeline Gontha</t>
+          <t>Tasya Aisyah Pratiwi Maasba</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>International Law</t>
+          <t>Medical Science</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -1266,12 +1274,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Narya Febrian Armansyah</t>
+          <t>Edeline Gontha</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1303,22 +1311,22 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Stephen Rosenbaum</t>
+          <t>Muhammad Narya Febrian Armansyah</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Human Rights Law, Antidiscrimination Law, Disability Rights Law</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>University of California</t>
+          <t>The Public Opinion and Social Behavior Research Group is established as an interdisciplinary research platform dedicated to understanding how public opinion is formed, expressed, and transformed into social behavior across digital and offline contexts.</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1340,22 +1348,22 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Rastiawaty, S.H., M.H.</t>
+          <t>Stephen Rosenbaum</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Law and Society</t>
+          <t>Human Rights Law, Antidiscrimination Law, Disability Rights Law</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>University of California</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1377,17 +1385,17 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Mutiah Wenda Juniar, S.H., LL.M.</t>
+          <t>Rastiawaty, S.H., M.H.</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>International Law, Disability Rights Law</t>
+          <t>Law and Society</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
@@ -1414,17 +1422,17 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Dr. Kadarudin, S.H., M.H.</t>
+          <t>Mutiah Wenda Juniar, S.H., LL.M.</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>International Law, Human Rights Law, Refugee Law</t>
+          <t>International Law, Disability Rights Law</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -1436,21 +1444,9 @@
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
       <c r="I18" s="12" t="n"/>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>my-orcid?orcid=0000-0002-4919-6169</t>
-        </is>
-      </c>
-      <c r="K18" s="11" t="inlineStr">
-        <is>
-          <t>5996291</t>
-        </is>
-      </c>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>57203506496</t>
-        </is>
-      </c>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="12" t="n"/>
       <c r="M18" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1463,17 +1459,17 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Iin Karita Sakharina, S.H., M.A.</t>
+          <t>Dr. Kadarudin, S.H., M.H.</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>International Law, Human Rights Law, Diplomatic Law</t>
+          <t>International Law, Human Rights Law, Refugee Law</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
@@ -1487,17 +1483,17 @@
       <c r="I19" s="12" t="n"/>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>0009-0001-6179-5439</t>
+          <t>my-orcid?orcid=0000-0002-4919-6169</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>6041015</t>
+          <t>5996291</t>
         </is>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>57216819104</t>
+          <t>57203506496</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
@@ -1510,18 +1506,50 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="11" t="n"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Prof. Dr. Iin Karita Sakharina, S.H., M.A.</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>The Public Opinion and Social Behavior Research Group is established as an interdisciplinary research platform dedicated to understanding how public opinion is formed, expressed, and transformed into social behavior across digital and offline contexts.</t>
+        </is>
+      </c>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
       <c r="I20" s="12" t="n"/>
-      <c r="J20" s="12" t="n"/>
-      <c r="K20" s="12" t="n"/>
-      <c r="L20" s="12" t="n"/>
-      <c r="M20" s="12" t="n"/>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>0009-0001-6179-5439</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>6041015</t>
+        </is>
+      </c>
+      <c r="L20" s="11" t="inlineStr">
+        <is>
+          <t>57216819104</t>
+        </is>
+      </c>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1710,15 +1738,32 @@
       <c r="L31" s="12" t="n"/>
       <c r="M31" s="12" t="n"/>
     </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
